--- a/data/31Maj-89ers-v-Towers.xlsx
+++ b/data/31Maj-89ers-v-Towers.xlsx
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:O127"/>
   <sheetData>
     <row r="1">
@@ -351,8 +351,10 @@
       <c r="D15" t="s">
         <v>16</v>
       </c>
-      <c r="E15" t="s">
-        <v>19</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LCDMFC</t>
+        </is>
       </c>
       <c r="F15" t="s">
         <v>20</v>
@@ -410,8 +412,10 @@
       <c r="D19" t="s">
         <v>16</v>
       </c>
-      <c r="E19" t="s">
-        <v>27</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>BCSCDC</t>
+        </is>
       </c>
       <c r="J19" t="s">
         <v>28</v>
@@ -533,8 +537,10 @@
       <c r="D31" t="s">
         <v>33</v>
       </c>
-      <c r="E31" t="s">
-        <v>34</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>DGSG</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -980,8 +986,10 @@
       <c r="D82" t="s">
         <v>16</v>
       </c>
-      <c r="E82" t="s">
-        <v>43</v>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>DCUCLC</t>
+        </is>
       </c>
       <c r="I82" t="s">
         <v>44</v>
